--- a/registry/DEEP_Agent_문서분류_레지스트리_v2.2.xlsx
+++ b/registry/DEEP_Agent_문서분류_레지스트리_v2.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsh930309/projects/dataFatory/registry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BD08CF-45D2-0D49-8161-DD7796FDF0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6EA8D6-3D14-9E4B-9326-E3CAC7F40F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21800" yWindow="-28200" windowWidth="51200" windowHeight="28200" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.안내" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="829">
   <si>
     <t>DEEP Agent 문서 분류 레지스트리 — 데이터 대시보드</t>
   </si>
@@ -2529,6 +2529,10 @@
   </si>
   <si>
     <t>잔액증명서</t>
+  </si>
+  <si>
+    <t>교체필요</t>
+    <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2538,7 +2542,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2724,6 +2728,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -2847,7 +2858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3036,18 +3047,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3334,7 +3348,7 @@
       <c r="F2" s="65"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="67" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="65"/>
@@ -3343,7 +3357,7 @@
       <c r="F3" s="65"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="66" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="65"/>
@@ -3352,7 +3366,7 @@
       <c r="F4" s="65"/>
     </row>
     <row r="6" spans="2:6" ht="20" customHeight="1">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="64" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="65"/>
@@ -3436,7 +3450,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="20" customHeight="1">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="64" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="65"/>
@@ -3476,7 +3490,7 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="20" customHeight="1">
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="64" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="65"/>
@@ -3549,7 +3563,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="20" customHeight="1">
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="64" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="65"/>
@@ -3644,7 +3658,7 @@
       </c>
     </row>
     <row r="36" spans="2:4" ht="20" customHeight="1">
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="64" t="s">
         <v>34</v>
       </c>
       <c r="C36" s="65"/>
@@ -3750,7 +3764,7 @@
       </c>
     </row>
     <row r="47" spans="2:4" ht="20" customHeight="1">
-      <c r="B47" s="67" t="s">
+      <c r="B47" s="64" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="65"/>
@@ -3823,7 +3837,7 @@
       </c>
     </row>
     <row r="55" spans="2:4" ht="20" customHeight="1">
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="64" t="s">
         <v>49</v>
       </c>
       <c r="C55" s="65"/>
@@ -3885,7 +3899,7 @@
       </c>
     </row>
     <row r="62" spans="2:4" ht="20" customHeight="1">
-      <c r="B62" s="67" t="s">
+      <c r="B62" s="64" t="s">
         <v>53</v>
       </c>
       <c r="C62" s="65"/>
@@ -4035,7 +4049,7 @@
       </c>
     </row>
     <row r="77" spans="2:4" ht="20" customHeight="1">
-      <c r="B77" s="67" t="s">
+      <c r="B77" s="64" t="s">
         <v>66</v>
       </c>
       <c r="C77" s="65"/>
@@ -4218,7 +4232,7 @@
       </c>
     </row>
     <row r="95" spans="2:6" ht="20" customHeight="1">
-      <c r="B95" s="67" t="s">
+      <c r="B95" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C95" s="65"/>
@@ -4305,11 +4319,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B4:F4"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="C102:F102"/>
@@ -4325,6 +4334,11 @@
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="C99:F99"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B4:F4"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14497,7 +14511,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16">
+    <row r="25" spans="1:6" ht="18">
       <c r="A25" s="52" t="s">
         <v>220</v>
       </c>
@@ -14513,7 +14527,9 @@
       <c r="E25" s="52" t="s">
         <v>778</v>
       </c>
-      <c r="F25" s="52"/>
+      <c r="F25" s="72" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="16">
       <c r="A26" s="52" t="s">

--- a/registry/DEEP_Agent_문서분류_레지스트리_v2.2.xlsx
+++ b/registry/DEEP_Agent_문서분류_레지스트리_v2.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsh930309/projects/dataFatory/registry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6EA8D6-3D14-9E4B-9326-E3CAC7F40F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD9FF90-5E25-714A-B846-A4623F6714B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.안내" sheetId="1" r:id="rId1"/>
@@ -3047,21 +3047,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3342,37 +3342,37 @@
       <c r="B2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
     </row>
     <row r="6" spans="2:6" ht="20" customHeight="1">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
     </row>
     <row r="7" spans="2:6" ht="22" customHeight="1">
       <c r="B7" s="53" t="s">
@@ -3450,11 +3450,11 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="20" customHeight="1">
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="56" t="s">
@@ -3490,11 +3490,11 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="20" customHeight="1">
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="56" t="s">
@@ -3563,11 +3563,11 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="20" customHeight="1">
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="56" t="s">
@@ -3658,11 +3658,11 @@
       </c>
     </row>
     <row r="36" spans="2:4" ht="20" customHeight="1">
-      <c r="B36" s="64" t="s">
+      <c r="B36" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="56" t="s">
@@ -3764,11 +3764,11 @@
       </c>
     </row>
     <row r="47" spans="2:4" ht="20" customHeight="1">
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="56" t="s">
@@ -3837,11 +3837,11 @@
       </c>
     </row>
     <row r="55" spans="2:4" ht="20" customHeight="1">
-      <c r="B55" s="64" t="s">
+      <c r="B55" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C55" s="65"/>
-      <c r="D55" s="65"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
     </row>
     <row r="56" spans="2:4">
       <c r="B56" s="56" t="s">
@@ -3899,11 +3899,11 @@
       </c>
     </row>
     <row r="62" spans="2:4" ht="20" customHeight="1">
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="65"/>
-      <c r="D62" s="65"/>
+      <c r="C62" s="66"/>
+      <c r="D62" s="66"/>
     </row>
     <row r="63" spans="2:4">
       <c r="B63" s="56" t="s">
@@ -4049,11 +4049,11 @@
       </c>
     </row>
     <row r="77" spans="2:4" ht="20" customHeight="1">
-      <c r="B77" s="64" t="s">
+      <c r="B77" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="65"/>
-      <c r="D77" s="65"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
     </row>
     <row r="78" spans="2:4">
       <c r="B78" s="56" t="s">
@@ -4232,13 +4232,13 @@
       </c>
     </row>
     <row r="95" spans="2:6" ht="20" customHeight="1">
-      <c r="B95" s="64" t="s">
+      <c r="B95" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="C95" s="65"/>
-      <c r="D95" s="65"/>
-      <c r="E95" s="65"/>
-      <c r="F95" s="65"/>
+      <c r="C95" s="66"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
+      <c r="F95" s="66"/>
     </row>
     <row r="96" spans="2:6" ht="30" customHeight="1">
       <c r="B96" s="62" t="s">
@@ -4319,6 +4319,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="C102:F102"/>
@@ -4335,10 +4339,6 @@
     <mergeCell ref="C99:F99"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B4:F4"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9799,7 +9799,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
@@ -10510,7 +10509,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:6" ht="21.75" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>524</v>
       </c>
@@ -10530,7 +10529,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:6" ht="21.75" customHeight="1">
       <c r="A37" s="7" t="s">
         <v>524</v>
       </c>
@@ -10550,7 +10549,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:6" ht="21.75" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>524</v>
       </c>
@@ -10570,7 +10569,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:6" ht="21.75" customHeight="1">
       <c r="A39" s="19" t="s">
         <v>524</v>
       </c>
@@ -10590,7 +10589,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:6" ht="21.75" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>527</v>
       </c>
@@ -10610,7 +10609,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:6" ht="21.75" customHeight="1">
       <c r="A41" s="7" t="s">
         <v>527</v>
       </c>
@@ -10630,7 +10629,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:6" ht="21.75" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>527</v>
       </c>
@@ -10650,7 +10649,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:6" ht="21.75" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>527</v>
       </c>
@@ -10670,7 +10669,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:6" ht="21.75" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>527</v>
       </c>
@@ -10690,7 +10689,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:6" ht="21.75" customHeight="1">
       <c r="A45" s="19" t="s">
         <v>527</v>
       </c>
@@ -10710,7 +10709,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:6" ht="21.75" customHeight="1">
       <c r="A46" s="11" t="s">
         <v>530</v>
       </c>
@@ -10730,7 +10729,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:6" ht="21.75" customHeight="1">
       <c r="A47" s="7" t="s">
         <v>530</v>
       </c>
@@ -10750,7 +10749,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:6" ht="21.75" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>530</v>
       </c>
@@ -10770,7 +10769,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:6" ht="21.75" customHeight="1">
       <c r="A49" s="7" t="s">
         <v>530</v>
       </c>
@@ -10790,7 +10789,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:6" ht="21.75" customHeight="1">
       <c r="A50" s="19" t="s">
         <v>530</v>
       </c>
@@ -10810,7 +10809,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="51" spans="1:6" ht="21.75" customHeight="1">
       <c r="A51" s="7" t="s">
         <v>533</v>
       </c>
@@ -10830,7 +10829,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="52" spans="1:6" ht="21.75" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>533</v>
       </c>
@@ -10850,7 +10849,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="53" spans="1:6" ht="21.75" customHeight="1">
       <c r="A53" s="7" t="s">
         <v>533</v>
       </c>
@@ -10870,7 +10869,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="54" spans="1:6" ht="21.75" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>533</v>
       </c>
@@ -10890,7 +10889,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="55" spans="1:6" ht="21.75" customHeight="1">
       <c r="A55" s="19" t="s">
         <v>533</v>
       </c>
@@ -10910,7 +10909,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="56" spans="1:6" ht="21.75" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>536</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:6" ht="21.75" customHeight="1">
       <c r="A57" s="7" t="s">
         <v>536</v>
       </c>
@@ -10950,7 +10949,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="58" spans="1:6" ht="21.75" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>536</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:6" ht="21.75" customHeight="1">
       <c r="A59" s="7" t="s">
         <v>536</v>
       </c>
@@ -10990,7 +10989,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="60" spans="1:6" ht="21.75" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>536</v>
       </c>
@@ -11010,7 +11009,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="61" spans="1:6" ht="21.75" customHeight="1">
       <c r="A61" s="7" t="s">
         <v>536</v>
       </c>
@@ -11030,7 +11029,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:6" ht="21.75" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>536</v>
       </c>
@@ -11050,7 +11049,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="63" spans="1:6" ht="21.75" customHeight="1">
       <c r="A63" s="19" t="s">
         <v>536</v>
       </c>
@@ -11070,7 +11069,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:6" ht="21.75" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>539</v>
       </c>
@@ -11090,7 +11089,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="65" spans="1:6" ht="21.75" customHeight="1">
       <c r="A65" s="7" t="s">
         <v>539</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:6" ht="21.75" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>539</v>
       </c>
@@ -11130,7 +11129,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="67" spans="1:6" ht="21.75" customHeight="1">
       <c r="A67" s="7" t="s">
         <v>539</v>
       </c>
@@ -11150,7 +11149,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="68" spans="1:6" ht="21.75" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>539</v>
       </c>
@@ -11170,7 +11169,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="69" spans="1:6" ht="21.75" customHeight="1">
       <c r="A69" s="19" t="s">
         <v>539</v>
       </c>
@@ -11190,7 +11189,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:6" ht="21.75" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>542</v>
       </c>
@@ -11210,7 +11209,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:6" ht="21.75" customHeight="1">
       <c r="A71" s="7" t="s">
         <v>542</v>
       </c>
@@ -11230,7 +11229,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:6" ht="21.75" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>542</v>
       </c>
@@ -11250,7 +11249,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="73" spans="1:6" ht="21.75" customHeight="1">
       <c r="A73" s="7" t="s">
         <v>542</v>
       </c>
@@ -11270,7 +11269,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="74" spans="1:6" ht="21.75" customHeight="1">
       <c r="A74" s="19" t="s">
         <v>542</v>
       </c>
@@ -11290,7 +11289,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:6" ht="21.75" customHeight="1">
       <c r="A75" s="7" t="s">
         <v>545</v>
       </c>
@@ -11310,7 +11309,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:6" ht="21.75" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>545</v>
       </c>
@@ -11330,7 +11329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="77" spans="1:6" ht="21.75" customHeight="1">
       <c r="A77" s="7" t="s">
         <v>545</v>
       </c>
@@ -11350,7 +11349,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:6" ht="21.75" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>545</v>
       </c>
@@ -11370,7 +11369,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="79" spans="1:6" ht="21.75" customHeight="1">
       <c r="A79" s="19" t="s">
         <v>545</v>
       </c>
@@ -11390,7 +11389,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:6" ht="21.75" customHeight="1">
       <c r="A80" s="11" t="s">
         <v>548</v>
       </c>
@@ -11410,7 +11409,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:6" ht="21.75" customHeight="1">
       <c r="A81" s="7" t="s">
         <v>548</v>
       </c>
@@ -11430,7 +11429,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:6" ht="21.75" customHeight="1">
       <c r="A82" s="11" t="s">
         <v>548</v>
       </c>
@@ -11450,7 +11449,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:6" ht="21.75" customHeight="1">
       <c r="A83" s="7" t="s">
         <v>548</v>
       </c>
@@ -11470,7 +11469,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:6" ht="21.75" customHeight="1">
       <c r="A84" s="19" t="s">
         <v>548</v>
       </c>
@@ -11490,7 +11489,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="85" spans="1:6" ht="21.75" customHeight="1">
       <c r="A85" s="7" t="s">
         <v>551</v>
       </c>
@@ -11510,7 +11509,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="86" spans="1:6" ht="21.75" customHeight="1">
       <c r="A86" s="11" t="s">
         <v>551</v>
       </c>
@@ -11530,7 +11529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:6" ht="21.75" customHeight="1">
       <c r="A87" s="7" t="s">
         <v>551</v>
       </c>
@@ -11550,7 +11549,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="88" spans="1:6" ht="21.75" customHeight="1">
       <c r="A88" s="11" t="s">
         <v>551</v>
       </c>
@@ -11570,7 +11569,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:6" ht="21.75" customHeight="1">
       <c r="A89" s="19" t="s">
         <v>551</v>
       </c>
@@ -11590,7 +11589,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:6" ht="21.75" customHeight="1">
       <c r="A90" s="11" t="s">
         <v>554</v>
       </c>
@@ -11610,7 +11609,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="91" spans="1:6" ht="21.75" customHeight="1">
       <c r="A91" s="7" t="s">
         <v>554</v>
       </c>
@@ -11630,7 +11629,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="92" spans="1:6" ht="21.75" customHeight="1">
       <c r="A92" s="11" t="s">
         <v>554</v>
       </c>
@@ -11650,7 +11649,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="93" spans="1:6" ht="21.75" customHeight="1">
       <c r="A93" s="7" t="s">
         <v>554</v>
       </c>
@@ -11670,7 +11669,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="94" spans="1:6" ht="21.75" customHeight="1">
       <c r="A94" s="19" t="s">
         <v>554</v>
       </c>
@@ -11690,7 +11689,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="95" spans="1:6" ht="21.75" customHeight="1">
       <c r="A95" s="7" t="s">
         <v>557</v>
       </c>
@@ -11710,7 +11709,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="96" spans="1:6" ht="21.75" customHeight="1">
       <c r="A96" s="11" t="s">
         <v>557</v>
       </c>
@@ -11730,7 +11729,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="97" spans="1:6" ht="21.75" customHeight="1">
       <c r="A97" s="7" t="s">
         <v>557</v>
       </c>
@@ -11750,7 +11749,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="98" spans="1:6" ht="21.75" customHeight="1">
       <c r="A98" s="11" t="s">
         <v>557</v>
       </c>
@@ -11770,7 +11769,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="99" spans="1:6" ht="21.75" customHeight="1">
       <c r="A99" s="19" t="s">
         <v>557</v>
       </c>
@@ -11790,7 +11789,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="100" spans="1:6" ht="21.75" customHeight="1">
       <c r="A100" s="11" t="s">
         <v>560</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="101" spans="1:6" ht="21.75" customHeight="1">
       <c r="A101" s="7" t="s">
         <v>560</v>
       </c>
@@ -11830,7 +11829,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="102" spans="1:6" ht="21.75" customHeight="1">
       <c r="A102" s="11" t="s">
         <v>560</v>
       </c>
@@ -11850,7 +11849,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="103" spans="1:6" ht="21.75" customHeight="1">
       <c r="A103" s="7" t="s">
         <v>563</v>
       </c>
@@ -11870,7 +11869,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="104" spans="1:6" ht="21.75" customHeight="1">
       <c r="A104" s="11" t="s">
         <v>563</v>
       </c>
@@ -11890,7 +11889,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="105" spans="1:6" ht="21.75" customHeight="1">
       <c r="A105" s="7" t="s">
         <v>563</v>
       </c>
@@ -11910,7 +11909,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="106" spans="1:6" ht="21.75" customHeight="1">
       <c r="A106" s="11" t="s">
         <v>566</v>
       </c>
@@ -11930,7 +11929,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="107" spans="1:6" ht="21.75" customHeight="1">
       <c r="A107" s="7" t="s">
         <v>566</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="108" spans="1:6" ht="21.75" customHeight="1">
       <c r="A108" s="19" t="s">
         <v>566</v>
       </c>
@@ -11970,7 +11969,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="109" spans="1:6" ht="21.75" customHeight="1">
       <c r="A109" s="7" t="s">
         <v>569</v>
       </c>
@@ -11990,7 +11989,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="110" spans="1:6" ht="21.75" customHeight="1">
       <c r="A110" s="11" t="s">
         <v>569</v>
       </c>
@@ -12010,7 +12009,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="111" spans="1:6" ht="21.75" customHeight="1">
       <c r="A111" s="7" t="s">
         <v>569</v>
       </c>
@@ -12030,7 +12029,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="112" spans="1:6" ht="21.75" customHeight="1">
       <c r="A112" s="11" t="s">
         <v>572</v>
       </c>
@@ -12050,7 +12049,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="113" spans="1:6" ht="21.75" customHeight="1">
       <c r="A113" s="7" t="s">
         <v>572</v>
       </c>
@@ -12070,7 +12069,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="114" spans="1:6" ht="21.75" customHeight="1">
       <c r="A114" s="11" t="s">
         <v>572</v>
       </c>
@@ -12090,7 +12089,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="19" t="s">
         <v>572</v>
       </c>
@@ -12110,7 +12109,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="116" spans="1:6" ht="21.75" customHeight="1">
       <c r="A116" s="11" t="s">
         <v>575</v>
       </c>
@@ -12130,7 +12129,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="117" spans="1:6" ht="21.75" customHeight="1">
       <c r="A117" s="7" t="s">
         <v>575</v>
       </c>
@@ -12450,7 +12449,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="133" spans="1:6" ht="21.75" customHeight="1">
       <c r="A133" s="7" t="s">
         <v>590</v>
       </c>
@@ -12470,7 +12469,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="134" spans="1:6" ht="21.75" customHeight="1">
       <c r="A134" s="11" t="s">
         <v>590</v>
       </c>
@@ -12490,7 +12489,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="135" spans="1:6" ht="21.75" customHeight="1">
       <c r="A135" s="7" t="s">
         <v>593</v>
       </c>
@@ -12510,7 +12509,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="136" spans="1:6" ht="21.75" customHeight="1">
       <c r="A136" s="11" t="s">
         <v>593</v>
       </c>
@@ -12530,7 +12529,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="137" spans="1:6" ht="21.75" customHeight="1">
       <c r="A137" s="7" t="s">
         <v>593</v>
       </c>
@@ -12550,7 +12549,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="138" spans="1:6" ht="21.75" customHeight="1">
       <c r="A138" s="19" t="s">
         <v>593</v>
       </c>
@@ -12570,7 +12569,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="139" spans="1:6" ht="21.75" customHeight="1">
       <c r="A139" s="7" t="s">
         <v>596</v>
       </c>
@@ -12590,7 +12589,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="140" spans="1:6" ht="21.75" customHeight="1">
       <c r="A140" s="11" t="s">
         <v>596</v>
       </c>
@@ -12610,7 +12609,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="141" spans="1:6" ht="21.75" customHeight="1">
       <c r="A141" s="7" t="s">
         <v>596</v>
       </c>
@@ -12630,7 +12629,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="142" spans="1:6" ht="21.75" customHeight="1">
       <c r="A142" s="11" t="s">
         <v>599</v>
       </c>
@@ -12650,7 +12649,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="143" spans="1:6" ht="21.75" customHeight="1">
       <c r="A143" s="7" t="s">
         <v>599</v>
       </c>
@@ -12670,7 +12669,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="144" spans="1:6" ht="21.75" customHeight="1">
       <c r="A144" s="11" t="s">
         <v>602</v>
       </c>
@@ -12690,7 +12689,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="145" spans="1:6" ht="21.75" customHeight="1">
       <c r="A145" s="7" t="s">
         <v>602</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="146" spans="1:6" ht="21.75" customHeight="1">
       <c r="A146" s="11" t="s">
         <v>602</v>
       </c>
@@ -12730,7 +12729,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="147" spans="1:6" ht="21.75" customHeight="1">
       <c r="A147" s="7" t="s">
         <v>605</v>
       </c>
@@ -12750,7 +12749,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="148" spans="1:6" ht="21.75" customHeight="1">
       <c r="A148" s="11" t="s">
         <v>605</v>
       </c>
@@ -12770,7 +12769,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="149" spans="1:6" ht="21.75" customHeight="1">
       <c r="A149" s="7" t="s">
         <v>605</v>
       </c>
@@ -12790,7 +12789,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="150" spans="1:6" ht="21.75" customHeight="1">
       <c r="A150" s="11" t="s">
         <v>605</v>
       </c>
@@ -12810,7 +12809,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="151" spans="1:6" ht="21.75" customHeight="1">
       <c r="A151" s="19" t="s">
         <v>605</v>
       </c>
@@ -12830,7 +12829,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="152" spans="1:6" ht="21.75" customHeight="1">
       <c r="A152" s="11" t="s">
         <v>608</v>
       </c>
@@ -12850,7 +12849,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="153" spans="1:6" ht="21.75" customHeight="1">
       <c r="A153" s="7" t="s">
         <v>608</v>
       </c>
@@ -12870,7 +12869,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="154" spans="1:6" ht="21.75" customHeight="1">
       <c r="A154" s="11" t="s">
         <v>611</v>
       </c>
@@ -12890,7 +12889,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="155" spans="1:6" ht="21.75" customHeight="1">
       <c r="A155" s="7" t="s">
         <v>611</v>
       </c>
@@ -12910,7 +12909,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="156" spans="1:6" ht="21.75" customHeight="1">
       <c r="A156" s="11" t="s">
         <v>611</v>
       </c>
@@ -12930,7 +12929,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="157" spans="1:6" ht="21.75" customHeight="1">
       <c r="A157" s="7" t="s">
         <v>611</v>
       </c>
@@ -12950,7 +12949,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="158" spans="1:6" ht="21.75" customHeight="1">
       <c r="A158" s="19" t="s">
         <v>611</v>
       </c>
@@ -12970,7 +12969,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="159" spans="1:6" ht="21.75" customHeight="1">
       <c r="A159" s="7" t="s">
         <v>614</v>
       </c>
@@ -12990,7 +12989,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="160" spans="1:6" ht="21.75" customHeight="1">
       <c r="A160" s="11" t="s">
         <v>614</v>
       </c>
@@ -13010,7 +13009,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="161" spans="1:6" ht="21.75" customHeight="1">
       <c r="A161" s="7" t="s">
         <v>614</v>
       </c>
@@ -13030,7 +13029,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="162" spans="1:6" ht="21.75" customHeight="1">
       <c r="A162" s="11" t="s">
         <v>617</v>
       </c>
@@ -13050,7 +13049,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="163" spans="1:6" ht="21.75" customHeight="1">
       <c r="A163" s="7" t="s">
         <v>617</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="164" spans="1:6" ht="21.75" customHeight="1">
       <c r="A164" s="19" t="s">
         <v>617</v>
       </c>
@@ -13090,7 +13089,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="165" spans="1:6" ht="21.75" customHeight="1">
       <c r="A165" s="7" t="s">
         <v>620</v>
       </c>
@@ -13110,7 +13109,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="166" spans="1:6" ht="21.75" customHeight="1">
       <c r="A166" s="19" t="s">
         <v>620</v>
       </c>
@@ -13130,7 +13129,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="167" spans="1:6" ht="21.75" customHeight="1">
       <c r="A167" s="7" t="s">
         <v>623</v>
       </c>
@@ -13150,7 +13149,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="168" spans="1:6" ht="21.75" customHeight="1">
       <c r="A168" s="11" t="s">
         <v>623</v>
       </c>
@@ -13170,7 +13169,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="169" spans="1:6" ht="21.75" customHeight="1">
       <c r="A169" s="7" t="s">
         <v>623</v>
       </c>
@@ -13190,7 +13189,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="170" spans="1:6" ht="21.75" customHeight="1">
       <c r="A170" s="11" t="s">
         <v>626</v>
       </c>
@@ -13210,7 +13209,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="171" spans="1:6" ht="21.75" customHeight="1">
       <c r="A171" s="7" t="s">
         <v>626</v>
       </c>
@@ -13230,7 +13229,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="172" spans="1:6" ht="21.75" customHeight="1">
       <c r="A172" s="11" t="s">
         <v>629</v>
       </c>
@@ -13250,7 +13249,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="173" spans="1:6" ht="21.75" customHeight="1">
       <c r="A173" s="7" t="s">
         <v>629</v>
       </c>
@@ -13270,7 +13269,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="174" spans="1:6" ht="21.75" customHeight="1">
       <c r="A174" s="11" t="s">
         <v>629</v>
       </c>
@@ -13290,7 +13289,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="175" spans="1:6" ht="21.75" customHeight="1">
       <c r="A175" s="19" t="s">
         <v>629</v>
       </c>
@@ -13310,7 +13309,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="176" spans="1:6" ht="21.75" customHeight="1">
       <c r="A176" s="11" t="s">
         <v>632</v>
       </c>
@@ -13330,7 +13329,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="177" spans="1:6" ht="21.75" customHeight="1">
       <c r="A177" s="7" t="s">
         <v>632</v>
       </c>
@@ -13350,7 +13349,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="178" spans="1:6" ht="21.75" customHeight="1">
       <c r="A178" s="19" t="s">
         <v>632</v>
       </c>
@@ -13370,7 +13369,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="179" spans="1:6" ht="21.75" customHeight="1">
       <c r="A179" s="7" t="s">
         <v>635</v>
       </c>
@@ -13390,7 +13389,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="180" spans="1:6" ht="21.75" customHeight="1">
       <c r="A180" s="11" t="s">
         <v>635</v>
       </c>
@@ -13410,7 +13409,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="181" spans="1:6" ht="21.75" customHeight="1">
       <c r="A181" s="7" t="s">
         <v>635</v>
       </c>
@@ -13430,7 +13429,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="182" spans="1:6" ht="21.75" customHeight="1">
       <c r="A182" s="11" t="s">
         <v>638</v>
       </c>
@@ -13450,7 +13449,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="183" spans="1:6" ht="21.75" customHeight="1">
       <c r="A183" s="7" t="s">
         <v>638</v>
       </c>
@@ -13470,7 +13469,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="184" spans="1:6" ht="21.75" customHeight="1">
       <c r="A184" s="11" t="s">
         <v>641</v>
       </c>
@@ -13490,7 +13489,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="185" spans="1:6" ht="21.75" customHeight="1">
       <c r="A185" s="7" t="s">
         <v>641</v>
       </c>
@@ -13510,7 +13509,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="186" spans="1:6" ht="21.75" customHeight="1">
       <c r="A186" s="11" t="s">
         <v>641</v>
       </c>
@@ -13530,7 +13529,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="187" spans="1:6" ht="21.75" customHeight="1">
       <c r="A187" s="7" t="s">
         <v>644</v>
       </c>
@@ -13550,7 +13549,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="21.75" hidden="1" customHeight="1">
+    <row r="188" spans="1:6" ht="21.75" customHeight="1">
       <c r="A188" s="11" t="s">
         <v>644</v>
       </c>
@@ -13596,21 +13595,7 @@
     <row r="212" ht="21.75" customHeight="1"/>
     <row r="213" ht="21.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:F188" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="BANK-01"/>
-        <filter val="BANK-02"/>
-        <filter val="BANK-04"/>
-        <filter val="BANK-05"/>
-        <filter val="BANK-07"/>
-        <filter val="MFG-01"/>
-        <filter val="MFG-02"/>
-        <filter val="MFG-03"/>
-        <filter val="MFG-04"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F188" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14527,7 +14512,7 @@
       <c r="E25" s="52" t="s">
         <v>778</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="64" t="s">
         <v>828</v>
       </c>
     </row>
